--- a/public/MCHD_Master_Workbook.xlsx
+++ b/public/MCHD_Master_Workbook.xlsx
@@ -7794,7 +7794,7 @@
         <v>74</v>
       </c>
       <c r="B9" s="58">
-        <v>46152.0</v>
+        <v>46146.0</v>
       </c>
       <c r="D9" s="59"/>
     </row>
@@ -7803,7 +7803,7 @@
         <v>75</v>
       </c>
       <c r="B10" s="58">
-        <v>46152.0</v>
+        <v>46146.0</v>
       </c>
       <c r="D10" s="59"/>
     </row>
@@ -7812,7 +7812,7 @@
         <v>76</v>
       </c>
       <c r="B11" s="59">
-        <v>46289.0</v>
+        <v>46203.0</v>
       </c>
     </row>
     <row r="12">
@@ -7820,7 +7820,7 @@
         <v>77</v>
       </c>
       <c r="B12" s="59">
-        <v>46202.0</v>
+        <v>46203.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/public/MCHD_Master_Workbook.xlsx
+++ b/public/MCHD_Master_Workbook.xlsx
@@ -7812,7 +7812,7 @@
         <v>76</v>
       </c>
       <c r="B11" s="59">
-        <v>46203.0</v>
+        <v>46204.0</v>
       </c>
     </row>
     <row r="12">
@@ -8805,8 +8805,8 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
